--- a/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
+++ b/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>23800</v>
+        <v>21200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -883,9 +883,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45433</v>
+      </c>
+      <c r="C4" s="4">
+        <v>200</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -909,9 +915,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45434</v>
+      </c>
+      <c r="C5" s="4">
+        <v>200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -935,9 +947,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45435</v>
+      </c>
+      <c r="C6" s="4">
+        <v>200</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -961,9 +979,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45436</v>
+      </c>
+      <c r="C7" s="4">
+        <v>200</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -987,9 +1011,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45437</v>
+      </c>
+      <c r="C8" s="4">
+        <v>200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1013,9 +1043,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45438</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1039,9 +1075,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45439</v>
+      </c>
+      <c r="C10" s="4">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1065,9 +1107,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45440</v>
+      </c>
+      <c r="C11" s="4">
+        <v>200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1091,9 +1139,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45442</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1117,9 +1171,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45443</v>
+      </c>
+      <c r="C13" s="4">
+        <v>200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1143,9 +1203,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45444</v>
+      </c>
+      <c r="C14" s="4">
+        <v>200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1169,9 +1235,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45445</v>
+      </c>
+      <c r="C15" s="4">
+        <v>200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1195,9 +1267,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45446</v>
+      </c>
+      <c r="C16" s="4">
+        <v>200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>

--- a/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
+++ b/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2800</v>
+        <v>8600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>21200</v>
+        <v>15400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -863,9 +863,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45467</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -895,9 +901,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45468</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -927,9 +939,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45472</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -959,9 +977,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45472</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -991,9 +1015,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45473</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1023,9 +1053,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45474</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1055,9 +1091,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45475</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1087,9 +1129,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45479</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1119,9 +1167,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45480</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1151,9 +1205,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45481</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1183,9 +1243,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45482</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1215,9 +1281,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45483</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1247,9 +1319,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45484</v>
+      </c>
+      <c r="G15" s="4">
+        <v>200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1299,9 +1377,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45448</v>
+      </c>
+      <c r="C17" s="4">
+        <v>200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1325,9 +1409,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45449</v>
+      </c>
+      <c r="C18" s="4">
+        <v>200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1351,9 +1441,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45451</v>
+      </c>
+      <c r="C19" s="4">
+        <v>200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1377,9 +1473,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45452</v>
+      </c>
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1403,9 +1505,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45454</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1429,9 +1537,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45455</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1455,9 +1569,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45456</v>
+      </c>
+      <c r="C23" s="4">
+        <v>200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1481,9 +1601,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45457</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1507,9 +1633,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45459</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1533,9 +1665,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45460</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1559,9 +1697,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45463</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1585,9 +1729,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45463</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1611,9 +1761,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45464</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1637,9 +1793,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45464</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1663,9 +1825,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45465</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1689,9 +1857,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45466</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
+++ b/LoanOfficer-A/2023/39 Haobijam Thasana.xlsx
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -801,7 +801,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8600</v>
+        <v>14000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15400</v>
+        <v>10000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45492</v>
+      </c>
+      <c r="K3" s="4">
+        <v>200</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -913,9 +919,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45492</v>
+      </c>
+      <c r="K4" s="4">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -951,9 +963,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45493</v>
+      </c>
+      <c r="K5" s="4">
+        <v>200</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -989,9 +1007,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45495</v>
+      </c>
+      <c r="K6" s="4">
+        <v>200</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>
@@ -1027,9 +1051,15 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45496</v>
+      </c>
+      <c r="K7" s="4">
+        <v>200</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
@@ -1065,9 +1095,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45497</v>
+      </c>
+      <c r="K8" s="4">
+        <v>200</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1103,9 +1139,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45497</v>
+      </c>
+      <c r="K9" s="4">
+        <v>200</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1141,9 +1183,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45499</v>
+      </c>
+      <c r="K10" s="4">
+        <v>200</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1179,9 +1227,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45499</v>
+      </c>
+      <c r="K11" s="4">
+        <v>200</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1217,9 +1271,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45500</v>
+      </c>
+      <c r="K12" s="4">
+        <v>200</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1357,9 +1417,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45485</v>
+      </c>
+      <c r="G16" s="4">
+        <v>200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1389,9 +1455,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45488</v>
+      </c>
+      <c r="G17" s="4">
+        <v>200</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1421,9 +1493,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45491</v>
+      </c>
+      <c r="G18" s="4">
+        <v>200</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1453,9 +1531,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45491</v>
+      </c>
+      <c r="G19" s="4">
+        <v>200</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1485,9 +1569,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G20" s="4">
+        <v>200</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1517,9 +1607,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1549,9 +1645,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1581,9 +1683,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1613,9 +1721,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1645,9 +1759,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1677,9 +1797,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G26" s="4">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1709,9 +1835,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G27" s="4">
+        <v>200</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1741,9 +1873,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G28" s="4">
+        <v>200</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1773,9 +1911,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G29" s="4">
+        <v>200</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1805,9 +1949,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G30" s="4">
+        <v>200</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1837,9 +1987,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G31" s="4">
+        <v>200</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1869,9 +2025,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45492</v>
+      </c>
+      <c r="G32" s="4">
+        <v>200</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>
